--- a/Regression-Handin-Template.xlsx
+++ b/Regression-Handin-Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51ffd66b5ca1e982/Studium/2_DHBW_Stuttgart/Auslandssemester/MA213B/seminars/MA213B-Seminar-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{F17588B3-D16F-4A1F-A72B-6CB49C5104B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C347ACD7-9424-B644-83C9-386F5AD87F44}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{F17588B3-D16F-4A1F-A72B-6CB49C5104B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0CD2C99-B929-1E4A-AF9E-056F75A33BB6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="15120" windowHeight="19000" xr2:uid="{447D43A1-1C16-467A-AB10-2FCAF1D1F1D6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Car #01</t>
   </si>
@@ -71,15 +71,69 @@
   </si>
   <si>
     <t>Price [€]</t>
+  </si>
+  <si>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>16578</t>
+  </si>
+  <si>
+    <t>237445</t>
+  </si>
+  <si>
+    <t>18942</t>
+  </si>
+  <si>
+    <t>17125</t>
+  </si>
+  <si>
+    <t>22742</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -194,16 +248,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,15 +587,15 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" style="9" customWidth="1"/>
     <col min="6" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="6"/>
@@ -544,28 +604,28 @@
       <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -573,85 +633,85 @@
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3">
-        <v>12.7</v>
-      </c>
-      <c r="C4" s="4">
-        <v>186</v>
-      </c>
-      <c r="D4" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>18220</v>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="C5" s="4">
-        <v>332</v>
-      </c>
-      <c r="D5" s="3">
-        <v>22.4</v>
-      </c>
-      <c r="E5" s="4">
-        <v>264917</v>
+      <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="3">
-        <v>11.6</v>
-      </c>
-      <c r="C6" s="4">
-        <v>187</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="E6" s="4">
-        <v>12812</v>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3">
-        <v>12.8</v>
-      </c>
-      <c r="C7" s="4">
-        <v>184</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6.6</v>
-      </c>
-      <c r="E7" s="4">
-        <v>15769</v>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="3">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="C8" s="4">
-        <v>210</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6.3</v>
-      </c>
-      <c r="E8" s="4">
-        <v>23797</v>
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
